--- a/docs/PipeDimensions.xlsx
+++ b/docs/PipeDimensions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\organ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758CF225-80E4-4BFE-AE91-87173D4BE1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD213C-3015-4E98-8B0F-D3AB816A448D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59490" yWindow="5925" windowWidth="43440" windowHeight="23445" activeTab="9" xr2:uid="{B2B28161-BA18-4FDD-93BC-6DFBB4B94DE8}"/>
+    <workbookView xWindow="58575" yWindow="9630" windowWidth="32040" windowHeight="23445" xr2:uid="{B2B28161-BA18-4FDD-93BC-6DFBB4B94DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="10" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="130">
   <si>
     <t>toe</t>
   </si>
@@ -420,6 +420,24 @@
   </si>
   <si>
     <t>8WPEF</t>
+  </si>
+  <si>
+    <t>Depths</t>
+  </si>
+  <si>
+    <t>S - contained</t>
+  </si>
+  <si>
+    <t>Volumes</t>
+  </si>
+  <si>
+    <t>Depth Total ft</t>
+  </si>
+  <si>
+    <t>S-contained d</t>
+  </si>
+  <si>
+    <t>count</t>
   </si>
 </sst>
 </file>
@@ -942,13 +960,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280EB543-2F7C-4155-A03A-5DA89403361F}">
-  <dimension ref="A3:P39"/>
+  <dimension ref="A2:AA39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="U2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -973,8 +996,29 @@
       <c r="P3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U3">
+        <v>96</v>
+      </c>
+      <c r="V3">
+        <v>90</v>
+      </c>
+      <c r="W3">
+        <v>48</v>
+      </c>
+      <c r="X3">
+        <v>24</v>
+      </c>
+      <c r="Y3">
+        <v>18</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>57</v>
       </c>
@@ -1002,8 +1046,17 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <v>4</v>
+      </c>
+      <c r="Y4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>61</v>
       </c>
@@ -1028,8 +1081,17 @@
       <c r="P5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="Y5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>62</v>
       </c>
@@ -1051,8 +1113,17 @@
       <c r="P6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="Z6">
+        <v>12</v>
+      </c>
+      <c r="AA6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>64</v>
       </c>
@@ -1068,8 +1139,14 @@
       <c r="P7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z7">
+        <v>24</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>66</v>
       </c>
@@ -1085,8 +1162,11 @@
       <c r="P8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>68</v>
       </c>
@@ -1105,8 +1185,17 @@
       <c r="P9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="Z9">
+        <v>12</v>
+      </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>71</v>
       </c>
@@ -1119,8 +1208,14 @@
       <c r="P10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z10">
+        <v>24</v>
+      </c>
+      <c r="AA10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>65</v>
       </c>
@@ -1133,8 +1228,11 @@
       <c r="P11" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="X11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>65</v>
       </c>
@@ -1147,8 +1245,11 @@
       <c r="P12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="X12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>72</v>
       </c>
@@ -1164,8 +1265,17 @@
       <c r="P13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="Z13">
+        <v>12</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>65</v>
       </c>
@@ -1178,8 +1288,14 @@
       <c r="P14" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z14">
+        <v>24</v>
+      </c>
+      <c r="AA14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>73</v>
       </c>
@@ -1195,8 +1311,11 @@
       <c r="P15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>74</v>
       </c>
@@ -1221,8 +1340,20 @@
       <c r="P16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>4</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>75</v>
       </c>
@@ -1247,8 +1378,20 @@
       <c r="P17" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V17">
+        <v>5</v>
+      </c>
+      <c r="W17">
+        <v>4</v>
+      </c>
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>79</v>
       </c>
@@ -1261,8 +1404,11 @@
       <c r="P18" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="W18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>81</v>
       </c>
@@ -1281,8 +1427,14 @@
       <c r="P19" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V19">
+        <v>3</v>
+      </c>
+      <c r="W19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>83</v>
       </c>
@@ -1307,8 +1459,20 @@
       <c r="P20" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V20">
+        <v>5</v>
+      </c>
+      <c r="W20">
+        <v>4</v>
+      </c>
+      <c r="X20">
+        <v>2</v>
+      </c>
+      <c r="Y20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>84</v>
       </c>
@@ -1324,8 +1488,17 @@
       <c r="P21" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V21">
+        <v>3</v>
+      </c>
+      <c r="Z21">
+        <v>12</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>65</v>
       </c>
@@ -1338,8 +1511,14 @@
       <c r="P22" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Z22">
+        <v>24</v>
+      </c>
+      <c r="AA22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>85</v>
       </c>
@@ -1358,8 +1537,17 @@
       <c r="P23" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U23">
+        <v>5</v>
+      </c>
+      <c r="V23">
+        <v>4</v>
+      </c>
+      <c r="W23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>86</v>
       </c>
@@ -1378,8 +1566,17 @@
       <c r="P24" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U24">
+        <v>5</v>
+      </c>
+      <c r="V24">
+        <v>4</v>
+      </c>
+      <c r="W24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>87</v>
       </c>
@@ -1395,8 +1592,14 @@
       <c r="P25" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V25">
+        <v>3</v>
+      </c>
+      <c r="W25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>88</v>
       </c>
@@ -1412,8 +1615,14 @@
       <c r="P26" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V26">
+        <v>3</v>
+      </c>
+      <c r="W26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>89</v>
       </c>
@@ -1429,8 +1638,11 @@
       <c r="P27" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>90</v>
       </c>
@@ -1446,8 +1658,11 @@
       <c r="P28" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>91</v>
       </c>
@@ -1455,12 +1670,64 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="S30" t="s">
+        <v>127</v>
+      </c>
+      <c r="U30">
+        <f>SUM(U4:U29)/12</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V30">
+        <f t="shared" ref="V30:Y30" si="0">SUM(V4:V29)/12</f>
+        <v>5.5</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="0"/>
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="X30">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="0"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S31" t="s">
+        <v>126</v>
+      </c>
+      <c r="U31">
+        <f>U30*(U3/12)*2</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="V31">
+        <f t="shared" ref="V31:Y31" si="1">V30*(V3/12)*2</f>
+        <v>82.5</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="1"/>
+        <v>23.333333333333332</v>
+      </c>
+      <c r="X31">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="Z31">
+        <f>SUM(U31:Y31)</f>
+        <v>124.99999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>68</v>
       </c>
@@ -1492,7 +1759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>58</v>
       </c>
@@ -1520,8 +1787,39 @@
       <c r="P33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="S33" t="s">
+        <v>129</v>
+      </c>
+      <c r="T33">
+        <f>SUM(U33:Z33)</f>
+        <v>49</v>
+      </c>
+      <c r="U33">
+        <f>COUNT(U4:U29)</f>
+        <v>2</v>
+      </c>
+      <c r="V33">
+        <f t="shared" ref="V33:Z33" si="2">COUNT(V4:V29)</f>
+        <v>18</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>97</v>
       </c>
@@ -1547,7 +1845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>100</v>
       </c>
@@ -1573,7 +1871,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>102</v>
       </c>
@@ -1590,7 +1888,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>81</v>
       </c>
@@ -1604,7 +1902,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
         <v>87</v>
       </c>
@@ -1615,7 +1913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>88</v>
       </c>
@@ -1749,11 +2047,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>3.17</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -3516,23 +3814,23 @@
         <v>61</v>
       </c>
       <c r="B68">
-        <f t="shared" ref="B68:B81" si="6">ROUND($B$2*POWER(2,-A68/17),2)</f>
+        <f t="shared" ref="B68:B79" si="6">ROUND($B$2*POWER(2,-A68/17),2)</f>
         <v>0.27</v>
       </c>
       <c r="C68">
-        <f t="shared" ref="C68:C81" si="7">ROUND($B$3+$B$5*POWER(2,-A68/12),1)</f>
+        <f t="shared" ref="C68:C79" si="7">ROUND($B$3+$B$5*POWER(2,-A68/12),1)</f>
         <v>9.1</v>
       </c>
       <c r="D68">
-        <f t="shared" ref="D68:D81" si="8">D67+B68+$D$2</f>
+        <f t="shared" ref="D68:D79" si="8">D67+B68+$D$2</f>
         <v>91.520000000000039</v>
       </c>
       <c r="E68">
-        <f t="shared" ref="E68:E81" si="9">IF(C68 &gt; $D$3, 0, IF(E67+B68+$D$2 &gt; $D$5, B68+$D$2, E67+B68+$D$2))</f>
+        <f t="shared" ref="E68:E79" si="9">IF(C68 &gt; $D$3, 0, IF(E67+B68+$D$2 &gt; $D$5, B68+$D$2, E67+B68+$D$2))</f>
         <v>3.33</v>
       </c>
       <c r="F68">
-        <f t="shared" ref="F68:F81" si="10">IF(C68 &gt; $D$4, 0, F69+B68+$G$2)</f>
+        <f t="shared" ref="F68:F79" si="10">IF(C68 &gt; $D$4, 0, F69+B68+$G$2)</f>
         <v>3.8400000000000003</v>
       </c>
     </row>
@@ -3813,7 +4111,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E81">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3930,7 +4228,7 @@
         <v>6.5</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F67" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
+        <f t="shared" ref="F7:F38" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3939,11 +4237,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B38" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>6</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C38" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -3997,11 +4295,11 @@
         <v>98.7</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D50" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D38" si="3">D8+B9+$D$2</f>
         <v>18.759999999999998</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E50" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E38" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>18.759999999999998</v>
       </c>
       <c r="F9">
@@ -4009,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <f t="shared" ref="G9:G44" si="5">C9+C8</f>
+        <f t="shared" ref="G9:G38" si="5">C9+C8</f>
         <v>202.9</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -4993,7 +5291,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5110,7 +5408,7 @@
         <v>6.5</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F67" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
+        <f t="shared" ref="F7:F50" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
         <v>0</v>
       </c>
     </row>
@@ -5119,11 +5417,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B50" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>6</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C50" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -5177,11 +5475,11 @@
         <v>98.7</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D50" si="3">D8+B9+$D$2</f>
         <v>18.759999999999998</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E50" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>18.759999999999998</v>
       </c>
       <c r="F9">
@@ -6527,7 +6825,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6644,7 +6942,7 @@
         <v>3.55</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F67" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
+        <f t="shared" ref="F7:F38" si="0">IF(C7 &gt; $D$4, 0, F8+B7+$G$2)</f>
         <v>0</v>
       </c>
     </row>
@@ -6653,11 +6951,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B38" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>3.17</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C38" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -6711,11 +7009,11 @@
         <v>98.7</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D38" si="3">D8+B9+$D$2</f>
         <v>10.26</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E38" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>10.26</v>
       </c>
       <c r="F9">
@@ -6723,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <f t="shared" ref="G9:G44" si="5">C9+C8</f>
+        <f t="shared" ref="G9:G38" si="5">C9+C8</f>
         <v>202.9</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -7647,7 +7945,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7794,11 +8092,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>1.63</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>18.3</v>
       </c>
       <c r="D8">
@@ -7852,11 +8150,11 @@
         <v>17.600000000000001</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
         <v>5.65</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>5.65</v>
       </c>
       <c r="F9">
@@ -9513,7 +9811,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9660,11 +9958,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>2.59</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>28.7</v>
       </c>
       <c r="D8">
@@ -9718,11 +10016,11 @@
         <v>27.4</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
         <v>8.5300000000000011</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>8.5300000000000011</v>
       </c>
       <c r="F9">
@@ -11385,7 +11683,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11556,11 +11854,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>3.26</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>38.1</v>
       </c>
       <c r="D8">
@@ -13275,7 +13573,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13446,11 +13744,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>4.32</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>53.2</v>
       </c>
       <c r="D8">
@@ -13504,11 +13802,11 @@
         <v>50.5</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
         <v>13.72</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>13.72</v>
       </c>
       <c r="F9">
@@ -15207,7 +15505,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15354,11 +15652,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>1.92</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>53.2</v>
       </c>
       <c r="D8">
@@ -15412,11 +15710,11 @@
         <v>50.5</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
         <v>6.51</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>6.51</v>
       </c>
       <c r="F9">
@@ -17073,7 +17371,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17220,11 +17518,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>1.92</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>53.2</v>
       </c>
       <c r="D8">
@@ -19242,7 +19540,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E79">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19368,11 +19666,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>6</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -21181,7 +21479,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21307,11 +21605,11 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <f t="shared" ref="B8:B68" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
+        <f t="shared" ref="B8:B67" si="1">ROUND($B$2*POWER(2,-A8/17),2)</f>
         <v>3.17</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:C68" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
+        <f t="shared" ref="C8:C67" si="2">ROUND($B$3+$B$5*POWER(2,-A8/12),1)</f>
         <v>104.2</v>
       </c>
       <c r="D8">
@@ -21365,11 +21663,11 @@
         <v>98.7</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:D68" si="3">D8+B9+$D$2</f>
+        <f t="shared" ref="D9:D67" si="3">D8+B9+$D$2</f>
         <v>10.26</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E68" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
+        <f t="shared" ref="E9:E67" si="4">IF(C9 &gt; $D$3, 0, IF(E8+B9+$D$2 &gt; $D$5, B9+$D$2, E8+B9+$D$2))</f>
         <v>10.26</v>
       </c>
       <c r="F9">
@@ -23068,7 +23366,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E7:E68">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
